--- a/input/mapping/045. OCB_GOLD_TCKH_TB_AR_BCN_DTL_QUANG.xlsx
+++ b/input/mapping/045. OCB_GOLD_TCKH_TB_AR_BCN_DTL_QUANG.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30408"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="241" documentId="11_CC4326AA2DB2FEBE8618AF05C8DEEEBE22C13C69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78215C93-EE23-4F61-8586-F8D23DD9F23A}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="11_CC4326AA2DB2FEBE8618AF05C8DEEEBE22C13C69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4211C22-9611-418E-ACF5-00B427F2609E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>code cu</t>
   </si>
   <si>
-    <t>tb_ar_bcn_dlt</t>
+    <t>tb_ar_bcn_dtl</t>
   </si>
   <si>
     <t>TABLEAU_TB_AR_BCN_DTL</t>
@@ -734,9 +734,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -755,7 +752,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -832,19 +828,25 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1205,256 +1207,256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="D3" s="17"/>
+      <c r="D3" s="15"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="41" t="s">
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="41"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="18" t="s">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="41"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="39"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="41"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1">
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1">
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
     </row>
     <row r="18" spans="2:9" ht="15" customHeight="1">
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
     </row>
     <row r="19" spans="2:9" ht="17.25" customHeight="1">
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="39"/>
     </row>
     <row r="21" spans="2:9" ht="15.75">
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" spans="2:9">
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="21" t="s">
+      <c r="B22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="2:9">
-      <c r="B23" s="25"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="21" t="s">
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="22"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="20"/>
     </row>
     <row r="24" spans="2:9">
-      <c r="B24" s="27"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="21" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="2:9">
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="21" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" spans="2:9">
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="21" t="s">
+      <c r="B26" s="29"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1477,73 +1479,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="40"/>
-      <c r="Z1" s="40"/>
-      <c r="AA1" s="40"/>
-      <c r="AB1" s="40"/>
-      <c r="AC1" s="40"/>
-      <c r="AD1" s="40"/>
-      <c r="AE1" s="40"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="43"/>
     </row>
     <row r="2" spans="1:31" ht="34.5" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="1:31" ht="45.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:31" ht="29.25" customHeight="1">
+      <c r="A3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1567,30 +1569,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F2" s="44" t="s">
@@ -1599,7 +1601,7 @@
       <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7" ht="61.5" customHeight="1">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -1620,7 +1622,7 @@
       <c r="G3" s="48"/>
     </row>
     <row r="4" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1641,7 +1643,7 @@
       <c r="G4" s="48"/>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1662,7 +1664,7 @@
       <c r="G5" s="48"/>
     </row>
     <row r="6" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1683,7 +1685,7 @@
       <c r="G6" s="48"/>
     </row>
     <row r="7" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1704,7 +1706,7 @@
       <c r="G7" s="48"/>
     </row>
     <row r="8" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1734,41 +1736,41 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="27" customHeight="1">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1786,10 +1788,10 @@
       <c r="F12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="15"/>
+      <c r="G12" s="13"/>
     </row>
     <row r="13" spans="1:7" ht="27" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>2</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1807,10 +1809,10 @@
       <c r="F13" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>3</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -1822,7 +1824,7 @@
       <c r="D14" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -1833,7 +1835,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="27" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -1845,7 +1847,7 @@
       <c r="D15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1856,7 +1858,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="27" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>5</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1879,7 +1881,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="27" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>6</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1902,7 +1904,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1925,7 +1927,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="27" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1948,48 +1950,48 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="27" customHeight="1">
-      <c r="A20" s="34">
+      <c r="A20" s="32">
         <v>9</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F20" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="33" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A21" s="38">
+      <c r="A21" s="36">
         <v>10</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D21" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F21" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="37" t="s">
+      <c r="G21" s="35" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2010,25 +2012,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2200,14 +2183,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF28AC8C-55E2-4D6D-9C6F-B7FAE7EFEE06}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9A0788B-CF64-48A4-8605-71542F82D565}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74FB0BAF-D755-405B-B5A3-880AF99BD78E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF28AC8C-55E2-4D6D-9C6F-B7FAE7EFEE06}"/>
 </file>